--- a/Temps_moyen_par_marathon_2026.xlsx
+++ b/Temps_moyen_par_marathon_2026.xlsx
@@ -916,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M64"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col width="23.36328125" customWidth="1" min="2" max="2"/>
@@ -929,6 +929,7 @@
     <col width="12.26953125" customWidth="1" style="95" min="10" max="10"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="101" t="inlineStr">
         <is>
@@ -936,6 +937,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="40" customHeight="1">
       <c r="B4" s="16" t="inlineStr">
         <is>
@@ -1564,10 +1566,18 @@
           <t>NN Marathon Rotterdam</t>
         </is>
       </c>
-      <c r="D28" s="133" t="n"/>
-      <c r="E28" s="114" t="n"/>
-      <c r="F28" s="109" t="n"/>
-      <c r="G28" s="135" t="n"/>
+      <c r="D28" s="133" t="n">
+        <v>15814</v>
+      </c>
+      <c r="E28" s="114" t="n">
+        <v>0.1843634259259259</v>
+      </c>
+      <c r="F28" s="109" t="n">
+        <v>0.08604166666666667</v>
+      </c>
+      <c r="G28" s="135" t="n">
+        <v>0.09648148148148149</v>
+      </c>
       <c r="H28" s="135" t="n"/>
       <c r="I28" s="136" t="n"/>
       <c r="J28" s="88" t="n"/>
